--- a/frontend/public/formats/enb_format.xlsx
+++ b/frontend/public/formats/enb_format.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11928B2A-CDE0-489D-A06C-DCD8AD0A3359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4B17AD-89BE-4F29-AC36-35316A4066DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDF84827-49C2-4B5C-A306-5A1A4B3B2D14}"/>
   </bookViews>
@@ -34,48 +34,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>SAP ID</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>JC name</t>
-  </si>
-  <si>
-    <t>JC ID</t>
-  </si>
-  <si>
-    <t>JC SAP ID</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Site Type</t>
-  </si>
-  <si>
-    <t>Device Type</t>
-  </si>
-  <si>
-    <t>Overall cNum count</t>
-  </si>
-  <si>
-    <t>Overall Cell Outage (sec)</t>
-  </si>
-  <si>
-    <t>Overall Cell Availability</t>
-  </si>
-  <si>
-    <t>Cells Up</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>circle</t>
+  </si>
+  <si>
+    <t>cmp</t>
+  </si>
+  <si>
+    <t>site_type</t>
+  </si>
+  <si>
+    <t>sap_id</t>
+  </si>
+  <si>
+    <t>jc_name</t>
+  </si>
+  <si>
+    <t>jc_id</t>
+  </si>
+  <si>
+    <t>jc_sap_id</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>site_type_excel</t>
+  </si>
+  <si>
+    <t>device_type</t>
+  </si>
+  <si>
+    <t>cnum_count</t>
+  </si>
+  <si>
+    <t>outage_sec</t>
+  </si>
+  <si>
+    <t>availability</t>
+  </si>
+  <si>
+    <t>cells_up</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh (East)</t>
   </si>
 </sst>
 </file>
@@ -91,12 +103,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -111,8 +129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,51 +446,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECAFB62-E27A-4917-87AC-E66CC7F34451}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/formats/enb_format.xlsx
+++ b/frontend/public/formats/enb_format.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4B17AD-89BE-4F29-AC36-35316A4066DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88F24A5-6532-4B74-AAB8-96C67DC6D160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDF84827-49C2-4B5C-A306-5A1A4B3B2D14}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="48">
   <si>
     <t>circle</t>
   </si>
@@ -72,9 +72,6 @@
     <t>outage_sec</t>
   </si>
   <si>
-    <t>availability</t>
-  </si>
-  <si>
     <t>cells_up</t>
   </si>
   <si>
@@ -87,16 +84,116 @@
     <t>Haryana</t>
   </si>
   <si>
-    <t>Uttar Pradesh (East)</t>
+    <t>UP East</t>
+  </si>
+  <si>
+    <t>Delhi-1 (West)</t>
+  </si>
+  <si>
+    <t>Delhi-2 (South)</t>
+  </si>
+  <si>
+    <t>Delhi-3 (Central-East)</t>
+  </si>
+  <si>
+    <t>Delhi-4 (North)</t>
+  </si>
+  <si>
+    <t>Faridabad (NCR)</t>
+  </si>
+  <si>
+    <t>Ghaziabad (NCR)</t>
+  </si>
+  <si>
+    <t>Gurgaon (NCR)</t>
+  </si>
+  <si>
+    <t>Noida (NCR)</t>
+  </si>
+  <si>
+    <t>Ambala</t>
+  </si>
+  <si>
+    <t>Hissar</t>
+  </si>
+  <si>
+    <t>Karnal</t>
+  </si>
+  <si>
+    <t>Panipat</t>
+  </si>
+  <si>
+    <t>Palwal</t>
+  </si>
+  <si>
+    <t>Rewari</t>
+  </si>
+  <si>
+    <t>Rohtak</t>
+  </si>
+  <si>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Bathinda</t>
+  </si>
+  <si>
+    <t>Chandigarh</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Ludhiana-1</t>
+  </si>
+  <si>
+    <t>Ludhiana-2</t>
+  </si>
+  <si>
+    <t>Pathankot</t>
+  </si>
+  <si>
+    <t>Patiala</t>
+  </si>
+  <si>
+    <t>Sangrur</t>
+  </si>
+  <si>
+    <t>Allahabad</t>
+  </si>
+  <si>
+    <t>Azamgarh</t>
+  </si>
+  <si>
+    <t>Faizabad</t>
+  </si>
+  <si>
+    <t>Gorakhpur</t>
+  </si>
+  <si>
+    <t>Raibareilly</t>
+  </si>
+  <si>
+    <t>Varanasi</t>
+  </si>
+  <si>
+    <t>overall_cell_availability</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,7 +214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -125,13 +222,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,71 +576,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECAFB62-E27A-4917-87AC-E66CC7F34451}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
+      <c r="B26" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
